--- a/Result/profitability/2387.xlsx
+++ b/Result/profitability/2387.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.71</v>
       </c>
       <c r="M2" t="n">
-        <v>1.175</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>15.23375</v>
+        <v>14.1525</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>0.995</v>
+        <v>0.6950000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>15.39875</v>
+        <v>15.26125</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.77375</v>
+        <v>0.6537499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>16.13125</v>
+        <v>15.78375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7250000000000001</v>
+        <v>0.7412500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>15.92625</v>
+        <v>15.43</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,13 +1137,13 @@
         <v>0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7987500000000001</v>
+        <v>0.6475000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>16.2325</v>
+        <v>15.8375</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6962499999999999</v>
+        <v>0.60375</v>
       </c>
       <c r="N7" t="n">
-        <v>16.52625</v>
+        <v>16.2575</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.92</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6975</v>
+        <v>0.6575</v>
       </c>
       <c r="N8" t="n">
-        <v>16.77625</v>
+        <v>16.7425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>1.02</v>
       </c>
       <c r="M10" t="n">
-        <v>0.845</v>
+        <v>0.8450000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>18.06875</v>
@@ -2026,7 +2026,7 @@
         <v>0.41</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9037499999999999</v>
+        <v>0.9037500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>18.6475</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2387</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4116</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3648</v>
+      </c>
+      <c r="E75" t="n">
+        <v>468</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="G75" t="n">
+        <v>41</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.01%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>39</v>
+      </c>
+      <c r="K75" t="n">
+        <v>33</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.1075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6530612244897959</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.2699999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02317596566523605</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.969999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2586319218241042</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
